--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - Relatório de Recusas  23.06.2025 a 29.06.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - Relatório de Recusas  23.06.2025 a 29.06.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8751EB-3FD2-4A5B-9761-337C4F44F1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5B898D-284E-4322-9410-1A6C41AA4A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,70 +51,88 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>133022249</t>
+    <t>Relatório de Recusas  23.06.2025 a 29.06.2025</t>
+  </si>
+  <si>
+    <t>133020014</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório Recusas Santander- 25.06.2025</t>
-  </si>
-  <si>
-    <t>133016638</t>
-  </si>
-  <si>
-    <t>133004445</t>
-  </si>
-  <si>
-    <t>133021281</t>
-  </si>
-  <si>
-    <t>133036268</t>
-  </si>
-  <si>
-    <t>133038310</t>
-  </si>
-  <si>
-    <t>133032350</t>
-  </si>
-  <si>
-    <t>133027814</t>
-  </si>
-  <si>
-    <t>133052365</t>
-  </si>
-  <si>
-    <t>133104287</t>
-  </si>
-  <si>
-    <t>133101251</t>
-  </si>
-  <si>
-    <t>133054036</t>
-  </si>
-  <si>
-    <t>133057676</t>
-  </si>
-  <si>
-    <t>133010146</t>
-  </si>
-  <si>
-    <t>133011327</t>
-  </si>
-  <si>
-    <t>133013688</t>
-  </si>
-  <si>
-    <t>133015065</t>
-  </si>
-  <si>
-    <t>133021474</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  23.06.2025 a 29.06.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  23.06.2025 a 29.06.2025v</t>
+    <t>Relatório Recusas Santander- 26.06.2025</t>
+  </si>
+  <si>
+    <t>133027027</t>
+  </si>
+  <si>
+    <t>133039213</t>
+  </si>
+  <si>
+    <t>133030152</t>
+  </si>
+  <si>
+    <t>133090611</t>
+  </si>
+  <si>
+    <t>133103112</t>
+  </si>
+  <si>
+    <t>132974835</t>
+  </si>
+  <si>
+    <t>133132930</t>
+  </si>
+  <si>
+    <t>132967091</t>
+  </si>
+  <si>
+    <t>133054354</t>
+  </si>
+  <si>
+    <t>133027559</t>
+  </si>
+  <si>
+    <t>133025490</t>
+  </si>
+  <si>
+    <t>133027435</t>
+  </si>
+  <si>
+    <t>133029421</t>
+  </si>
+  <si>
+    <t>133031512</t>
+  </si>
+  <si>
+    <t>133031614</t>
+  </si>
+  <si>
+    <t>133032552</t>
+  </si>
+  <si>
+    <t>133035269</t>
+  </si>
+  <si>
+    <t>133035371</t>
+  </si>
+  <si>
+    <t>133035554</t>
+  </si>
+  <si>
+    <t>133035749</t>
+  </si>
+  <si>
+    <t>133037610</t>
+  </si>
+  <si>
+    <t>133038562</t>
+  </si>
+  <si>
+    <t>133038981</t>
+  </si>
+  <si>
+    <t>133040551</t>
   </si>
 </sst>
 </file>
@@ -521,7 +539,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -553,16 +571,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -571,16 +589,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -589,16 +607,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -607,16 +625,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -625,16 +643,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>27</v>
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -643,16 +661,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -661,16 +679,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -679,16 +697,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -697,16 +715,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>27</v>
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -715,16 +733,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>27</v>
+        <v>10</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -733,16 +751,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -751,16 +769,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -769,16 +787,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>27</v>
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -787,16 +805,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -805,16 +823,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>27</v>
+        <v>10</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -823,16 +841,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -841,16 +859,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>27</v>
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -858,32 +876,148 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D20" s="6"/>
+      <c r="A20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D21" s="6"/>
+      <c r="A21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D22" s="6"/>
+      <c r="A22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D23" s="6"/>
+      <c r="A23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D29" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
